--- a/backup/alp/淮安巨石运维问题.xlsx
+++ b/backup/alp/淮安巨石运维问题.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>问题描述</t>
   </si>
@@ -37,10 +37,23 @@
     <t>时间</t>
   </si>
   <si>
+    <t>状态</t>
+  </si>
+  <si>
     <t>制毡生产任务，派工报错修改</t>
   </si>
   <si>
+    <t>已完成</t>
+  </si>
+  <si>
     <t>克重强力可燃物保存没反应修改</t>
+  </si>
+  <si>
+    <t>页面显示卡顿问题，早晨查询帆软报表导致锁表</t>
+  </si>
+  <si>
+    <t>检测中心那边反映这个系统搜索产品类型转个几分钟才能出来。
+成品物性检测(SAP)页面，产品类型选择直接纱</t>
   </si>
 </sst>
 </file>
@@ -693,11 +706,11 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1010,36 +1023,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="29" customHeight="1" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="29" customHeight="1" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="67.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.75" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="17.625" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:2">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3">
         <v>46137</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" customHeight="1" spans="1:2">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3">
         <v>46137</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46139</v>
       </c>
     </row>
   </sheetData>

--- a/backup/alp/淮安巨石运维问题.xlsx
+++ b/backup/alp/淮安巨石运维问题.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>问题描述</t>
   </si>
@@ -40,20 +40,31 @@
     <t>状态</t>
   </si>
   <si>
+    <t>是否日志</t>
+  </si>
+  <si>
+    <t>用时</t>
+  </si>
+  <si>
     <t>制毡生产任务，派工报错修改</t>
   </si>
   <si>
     <t>已完成</t>
   </si>
   <si>
-    <t>克重强力可燃物保存没反应修改</t>
+    <t>否</t>
   </si>
   <si>
-    <t>页面显示卡顿问题，早晨查询帆软报表导致锁表</t>
+    <t>克重强力可燃物保存没反应修改</t>
   </si>
   <si>
     <t>检测中心那边反映这个系统搜索产品类型转个几分钟才能出来。
 成品物性检测(SAP)页面，产品类型选择直接纱</t>
+  </si>
+  <si>
+    <t>车间检测，cpk统计查询慢。查询条件：
+2026-01-01 到 2026-01-31
+产线选择 101产线</t>
   </si>
 </sst>
 </file>
@@ -422,7 +433,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -440,6 +451,32 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -569,7 +606,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -581,34 +618,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
@@ -693,7 +730,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -706,11 +743,20 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1023,65 +1069,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="29" customHeight="1" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="29" customHeight="1" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="67.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="11.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
+    <row r="2" customHeight="1" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3">
         <v>46137</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
+    <row r="3" customHeight="1" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3">
         <v>46137</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="2" t="s">
+    <row r="4" customHeight="1" spans="1:5">
+      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46139</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3">
-        <v>46136</v>
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="7">
+        <v>2.5</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>7</v>
+    <row r="5" ht="50" customHeight="1" spans="1:5">
+      <c r="A5" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="3">
         <v>46139</v>
       </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="8"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E4:E5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/backup/alp/淮安巨石运维问题.xlsx
+++ b/backup/alp/淮安巨石运维问题.xlsx
@@ -52,7 +52,7 @@
     <t>已完成</t>
   </si>
   <si>
-    <t>否</t>
+    <t>是</t>
   </si>
   <si>
     <t>克重强力可燃物保存没反应修改</t>

--- a/backup/alp/淮安巨石运维问题.xlsx
+++ b/backup/alp/淮安巨石运维问题.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>问题描述</t>
   </si>
@@ -65,6 +65,18 @@
     <t>车间检测，cpk统计查询慢。查询条件：
 2026-01-01 到 2026-01-31
 产线选择 101产线</t>
+  </si>
+  <si>
+    <t>检装整托抽检，保存报错</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>线密度品种统计报表卡顿</t>
+  </si>
+  <si>
+    <t>未完成</t>
   </si>
 </sst>
 </file>
@@ -817,6 +829,95 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>683260</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>328295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9620250" y="2108200"/>
+          <a:ext cx="683260" cy="328295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>629920</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>328295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9620250" y="2476500"/>
+          <a:ext cx="629920" cy="328295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1069,15 +1170,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="29" customHeight="1" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="29" customHeight="1" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="67.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.625" style="4" customWidth="1"/>
     <col min="5" max="5" width="11.125" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="12.375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -1162,6 +1264,37 @@
         <v>7</v>
       </c>
       <c r="E5" s="8"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46148</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46148</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1170,6 +1303,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
